--- a/ctl-site/src/assets/PROJETOS/PROJETO_4.xlsx
+++ b/ctl-site/src/assets/PROJETOS/PROJETO_4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\ctl-site\ctl-site\src\assets\PROJETOS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9be54d10f24db4ff/CTL site/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21F96A1F-141D-42A2-ACBF-1AB18415E41A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B45CC9BD-76B9-4752-8F18-6BAB3E102B28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet_TEST_1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="3">
+  <futureMetadata name="XLRICHVALUE" count="1">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -37,31 +37,11 @@
         </ext>
       </extLst>
     </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="1"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="2"/>
-        </ext>
-      </extLst>
-    </bk>
   </futureMetadata>
-  <valueMetadata count="3">
+  <valueMetadata count="1">
     <bk>
       <rc t="1" v="0"/>
     </bk>
-    <bk>
-      <rc t="1" v="1"/>
-    </bk>
-    <bk>
-      <rc t="1" v="2"/>
-    </bk>
   </valueMetadata>
 </metadata>
 </file>
@@ -69,10 +49,11 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
-    <t>Título Projeto 4</t>
+    <t>Conect'arte</t>
   </si>
   <si>
-    <t>Olá isto é um texto novo</t>
+    <t>Conect’arte é um projeto educativo, cultural, social e intergeracional promovido pelas Oficinas de Música, que tem como principal objetivo promover a ligação entre crianças e adultos através da música.
+Esta iniciativa pretende sensibilizar os intervenientes para a dimensão lúdica, social e formativa da música, valorizando o desenvolvimento pessoal, a expressão artística e o fortalecimento das relações interpessoais. O projeto aposta na formação musical individual e coletiva, estimulando a partilha de experiências, a inclusão social e o convívio entre diferentes gerações.</t>
   </si>
 </sst>
 </file>
@@ -108,8 +89,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -168,17 +152,9 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="3">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
   <rv s="0">
     <v>0</v>
-    <v>5</v>
-  </rv>
-  <rv s="0">
-    <v>1</v>
-    <v>5</v>
-  </rv>
-  <rv s="0">
-    <v>2</v>
     <v>5</v>
   </rv>
 </rvData>
@@ -196,8 +172,6 @@
 <file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
 <richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <rel r:id="rId1"/>
-  <rel r:id="rId2"/>
-  <rel r:id="rId3"/>
 </richValueRels>
 </file>
 
@@ -465,36 +439,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.109375" customWidth="1"/>
-    <col min="2" max="2" width="59.33203125" customWidth="1"/>
-    <col min="3" max="3" width="41.33203125" customWidth="1"/>
-    <col min="4" max="4" width="37.6640625" customWidth="1"/>
+    <col min="1" max="1" width="20.140625" customWidth="1"/>
+    <col min="2" max="2" width="59.28515625" customWidth="1"/>
+    <col min="3" max="3" width="41.28515625" customWidth="1"/>
+    <col min="4" max="4" width="37.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="113.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="113.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="64.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C2" t="e" vm="2">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="78.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C3" t="e" vm="3">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="78.599999999999994" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:3" ht="64.150000000000006" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:3" ht="78.599999999999994" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:3" ht="78.599999999999994" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/ctl-site/src/assets/PROJETOS/PROJETO_4.xlsx
+++ b/ctl-site/src/assets/PROJETOS/PROJETO_4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9be54d10f24db4ff/CTL site/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\ctl-site\ctl-site\src\assets\PROJETOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B45CC9BD-76B9-4752-8F18-6BAB3E102B28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EAB8ECE-16B1-4304-95B5-7E456B1A82D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet_TEST_1" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>Conect'arte</t>
   </si>
@@ -55,12 +55,29 @@
     <t>Conect’arte é um projeto educativo, cultural, social e intergeracional promovido pelas Oficinas de Música, que tem como principal objetivo promover a ligação entre crianças e adultos através da música.
 Esta iniciativa pretende sensibilizar os intervenientes para a dimensão lúdica, social e formativa da música, valorizando o desenvolvimento pessoal, a expressão artística e o fortalecimento das relações interpessoais. O projeto aposta na formação musical individual e coletiva, estimulando a partilha de experiências, a inclusão social e o convívio entre diferentes gerações.</t>
   </si>
+  <si>
+    <t>TÍTULO
+Aparece no cartão e na dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DESCRIÇÃO
+Aparece no cartão e dialog. </t>
+  </si>
+  <si>
+    <t>IMAGENS
+A primeira aparece no cartão.
+As seguintes aparecem no carrossel da dialog.</t>
+  </si>
+  <si>
+    <t>LINK YOUTUBE
+Substitui o carrossel da dialog.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -68,16 +85,30 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -85,14 +116,32 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -438,29 +487,44 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.140625" customWidth="1"/>
-    <col min="2" max="2" width="59.28515625" customWidth="1"/>
-    <col min="3" max="3" width="41.28515625" customWidth="1"/>
-    <col min="4" max="4" width="37.7109375" customWidth="1"/>
+    <col min="1" max="1" width="20.109375" customWidth="1"/>
+    <col min="2" max="3" width="59.33203125" customWidth="1"/>
+    <col min="4" max="4" width="41.33203125" customWidth="1"/>
+    <col min="5" max="5" width="37.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="113.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="113.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="e" vm="1">
+      <c r="C2" s="1"/>
+      <c r="D2" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="64.150000000000006" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:3" ht="78.599999999999994" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="1:3" ht="78.599999999999994" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:4" ht="64.2" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:4" ht="78.599999999999994" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="5" spans="1:4" ht="78.599999999999994" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
